--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97373</v>
+        <v>97376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97373</v>
+        <v>97376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97373</v>
+        <v>97376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97373</v>
+        <v>97376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97373</v>
+        <v>97376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97373</v>
+        <v>97376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97376</v>
+        <v>97377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97376</v>
+        <v>97377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97376</v>
+        <v>97377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97376</v>
+        <v>97377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97376</v>
+        <v>97377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97376</v>
+        <v>97377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97377</v>
+        <v>97382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97377</v>
+        <v>97382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97377</v>
+        <v>97382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97377</v>
+        <v>97382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97377</v>
+        <v>97382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97377</v>
+        <v>97382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,44 +680,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132227660</v>
+        <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>97224</v>
+        <v>96564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>581</v>
+        <v>530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trubbklockmossa</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Encalypta mutica</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>I.Hagen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>med kapsel</t>
@@ -727,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+          <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505129</v>
+        <v>505141</v>
       </c>
       <c r="R2" t="n">
-        <v>6664591</v>
+        <v>6664584</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,17 +753,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Förekommer inom 1 dm2</t>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,42 +776,37 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Gruva</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Före detta kalkbrott</t>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Kalksten</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bar jord nedanför liten brant</t>
+          <t>Limestone</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132227660</t>
+          <t>https://artportalen.se/Sighting/130191861</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132228362</v>
+        <v>132227660</v>
       </c>
       <c r="B3" t="n">
         <v>97224</v>
@@ -849,12 +836,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -870,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505126</v>
+        <v>505129</v>
       </c>
       <c r="R3" t="n">
-        <v>6664592</v>
+        <v>6664591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,6 +895,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Förekommer inom 1 dm2</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -930,7 +922,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bar jord i sydvästvänd slänt</t>
+          <t>Bar jord nedanför liten brant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,42 +939,50 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132228362</t>
+          <t>https://artportalen.se/Sighting/132227660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124140322</v>
+        <v>132228362</v>
       </c>
       <c r="B4" t="n">
-        <v>97382</v>
+        <v>97224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hårklockmossa</t>
+          <t>Trubbklockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Encalypta spathulata</t>
+          <t>Encalypta mutica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Müll.Hal.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>I.Hagen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>med kapsel</t>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505147</v>
+        <v>505126</v>
       </c>
       <c r="R4" t="n">
-        <v>6664590</v>
+        <v>6664592</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,17 +1026,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Förekom inom 11 dm2. Kollekt sparad.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,17 +1051,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Nedlagt kalkbrott</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Lera (&lt; 0,002 mm)</t>
+          <t>Före detta kalkbrott</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Clay (&lt; 0,002 mm) # Bar jord i sydvästvänd slänt</t>
+          <t>Bar jord i sydvästvänd slänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,13 +1073,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124140322</t>
+          <t>https://artportalen.se/Sighting/132228362</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124140658</v>
+        <v>124140322</v>
       </c>
       <c r="B5" t="n">
         <v>97382</v>
@@ -1132,10 +1122,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505152</v>
+        <v>505147</v>
       </c>
       <c r="R5" t="n">
-        <v>6664595</v>
+        <v>6664590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,7 +1162,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Förekom inom 2 dm2. Kollekt sparad.</t>
+          <t>Förekom inom 11 dm2. Kollekt sparad.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,9 +1185,14 @@
           <t>Nedlagt kalkbrott</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Lera (&lt; 0,002 mm)</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bar jord på ett block</t>
+          <t>Clay (&lt; 0,002 mm) # Bar jord i sydvästvänd slänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1214,13 +1209,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124140658</t>
+          <t>https://artportalen.se/Sighting/124140322</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694795</v>
+        <v>124140658</v>
       </c>
       <c r="B6" t="n">
         <v>97382</v>
@@ -1263,10 +1258,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505135</v>
+        <v>505152</v>
       </c>
       <c r="R6" t="n">
-        <v>6664587</v>
+        <v>6664595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,17 +1288,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Förekom inom 20 dm2.</t>
+          <t>Förekom inom 2 dm2. Kollekt sparad.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,14 +1321,9 @@
           <t>Nedlagt kalkbrott</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Lera (&lt; 0,002 mm)</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Clay (&lt; 0,002 mm) #  Bar jord i sydvästvänd slänt</t>
+          <t>Bar jord på ett block</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,13 +1340,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129694795</t>
+          <t>https://artportalen.se/Sighting/124140658</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132225993</v>
+        <v>129694795</v>
       </c>
       <c r="B7" t="n">
         <v>97382</v>
@@ -1384,16 +1374,8 @@
           <t>Müll.Hal.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>med kapsel</t>
@@ -1407,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505142</v>
+        <v>505135</v>
       </c>
       <c r="R7" t="n">
-        <v>6664595</v>
+        <v>6664587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1437,17 +1419,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Förekommer inom 2 dm2</t>
+          <t>Förekom inom 20 dm2.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,12 +1449,17 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Före detta kalkbrott</t>
+          <t>Nedlagt kalkbrott</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Lera (&lt; 0,002 mm)</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bar jord intill granstubbe</t>
+          <t>Clay (&lt; 0,002 mm) #  Bar jord i sydvästvänd slänt</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1489,13 +1476,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132225993</t>
+          <t>https://artportalen.se/Sighting/129694795</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132226930</v>
+        <v>132225993</v>
       </c>
       <c r="B8" t="n">
         <v>97382</v>
@@ -1525,7 +1512,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1546,10 +1533,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505146</v>
+        <v>505142</v>
       </c>
       <c r="R8" t="n">
-        <v>6664605</v>
+        <v>6664595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1586,7 +1573,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förekommer inom 1 dm2</t>
+          <t>Förekommer inom 2 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,7 +1598,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bar jord på block</t>
+          <t>Bar jord intill granstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1628,13 +1615,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132226930</t>
+          <t>https://artportalen.se/Sighting/132225993</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132228649</v>
+        <v>132226930</v>
       </c>
       <c r="B9" t="n">
         <v>97382</v>
@@ -1664,7 +1651,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1685,10 +1672,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505127</v>
+        <v>505146</v>
       </c>
       <c r="R9" t="n">
-        <v>6664595</v>
+        <v>6664605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1725,7 +1712,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förekommer inom 10 dm2</t>
+          <t>Förekommer inom 1 dm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1750,7 +1737,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bar jord i sydvästvänd slänt, intill murkna vedrester</t>
+          <t>Bar jord på block</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1767,48 +1754,64 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132228649</t>
+          <t>https://artportalen.se/Sighting/132226930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130191015</v>
+        <v>132228649</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>97382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>582</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hårklockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Encalypta spathulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Müll.Hal.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norsberget, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505133</v>
+        <v>505127</v>
       </c>
       <c r="R10" t="n">
         <v>6664595</v>
@@ -1838,12 +1841,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förekommer inom 10 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,87 +1860,84 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bar jord i sydvästvänd slänt, intill murkna vedrester</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130191015</t>
+          <t>https://artportalen.se/Sighting/132228649</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124131064</v>
+        <v>130191015</v>
       </c>
       <c r="B11" t="n">
-        <v>97811</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2604</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+          <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505137</v>
+        <v>505133</v>
       </c>
       <c r="R11" t="n">
-        <v>6664578</v>
+        <v>6664595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1959,27 +1964,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1988,44 +1978,48 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Basisk bergart (grönsten)</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Basic rock # Mycket stort block</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124131064</t>
+          <t>https://artportalen.se/Sighting/130191015</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132225944</v>
+        <v>124131064</v>
       </c>
       <c r="B12" t="n">
-        <v>97888</v>
+        <v>97811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2061,10 +2055,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505140</v>
+        <v>505137</v>
       </c>
       <c r="R12" t="n">
-        <v>6664586</v>
+        <v>6664578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2091,12 +2085,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2114,24 +2118,14 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Gruva</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Före detta kalkbrott</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Block (&gt; 200 mm)</t>
+          <t>Basisk bergart (grönsten)</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Rock (&gt; 200 mm) # Stort block</t>
+          <t>Basic rock # Mycket stort block</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2148,16 +2142,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132225944</t>
+          <t>https://artportalen.se/Sighting/124131064</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124131425</v>
+        <v>132225944</v>
       </c>
       <c r="B13" t="n">
-        <v>96437</v>
+        <v>97888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2165,21 +2159,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2193,10 +2187,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505154</v>
+        <v>505140</v>
       </c>
       <c r="R13" t="n">
-        <v>6664604</v>
+        <v>6664586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2223,22 +2217,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2251,14 +2240,24 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Basisk bergart (grönsten)</t>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Basic rock # Klippvägg</t>
+          <t>Rock (&gt; 200 mm) # Stort block</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2275,13 +2274,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124131425</t>
+          <t>https://artportalen.se/Sighting/132225944</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726919</v>
+        <v>124131425</v>
       </c>
       <c r="B14" t="n">
         <v>96437</v>
@@ -2320,10 +2319,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505124</v>
+        <v>505154</v>
       </c>
       <c r="R14" t="n">
-        <v>6664590</v>
+        <v>6664604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2350,12 +2349,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2375,7 +2384,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Basic rock</t>
+          <t>Basic rock # Klippvägg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2392,13 +2401,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129726919</t>
+          <t>https://artportalen.se/Sighting/124131425</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726980</v>
+        <v>129726919</v>
       </c>
       <c r="B15" t="n">
         <v>96437</v>
@@ -2437,10 +2446,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505145</v>
+        <v>505124</v>
       </c>
       <c r="R15" t="n">
-        <v>6664597</v>
+        <v>6664590</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2509,16 +2518,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129726980</t>
+          <t>https://artportalen.se/Sighting/129726919</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694622</v>
+        <v>129726980</v>
       </c>
       <c r="B16" t="n">
-        <v>96426</v>
+        <v>96437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2526,21 +2535,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2550,14 +2559,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norsberget, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505148</v>
+        <v>505145</v>
       </c>
       <c r="R16" t="n">
-        <v>6664580</v>
+        <v>6664597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2626,51 +2635,55 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129694622</t>
+          <t>https://artportalen.se/Sighting/129726980</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130189264</v>
+        <v>129694622</v>
       </c>
       <c r="B17" t="n">
-        <v>93189</v>
+        <v>96426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>2671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505170</v>
+        <v>505148</v>
       </c>
       <c r="R17" t="n">
-        <v>6664585</v>
+        <v>6664580</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2697,12 +2710,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2711,33 +2724,44 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Basic rock</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130189264</t>
+          <t>https://artportalen.se/Sighting/129694622</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130188532</v>
+        <v>130189264</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2745,21 +2769,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2769,10 +2793,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505194</v>
+        <v>505170</v>
       </c>
       <c r="R18" t="n">
-        <v>6664573</v>
+        <v>6664585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2830,16 +2854,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130188532</t>
+          <t>https://artportalen.se/Sighting/130189264</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1404137</v>
+        <v>130188532</v>
       </c>
       <c r="B19" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2847,46 +2871,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505148</v>
+        <v>505194</v>
       </c>
       <c r="R19" t="n">
-        <v>6664594</v>
+        <v>6664573</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2910,12 +2925,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2926,61 +2941,65 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1404137</t>
+          <t>https://artportalen.se/Sighting/130188532</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1339311</v>
+        <v>1404137</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norsberget, Dlr</t>
@@ -3053,16 +3072,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1339311</t>
+          <t>https://artportalen.se/Sighting/1404137</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129694667</v>
+        <v>1339311</v>
       </c>
       <c r="B21" t="n">
-        <v>93300</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,44 +3089,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505166</v>
+        <v>505148</v>
       </c>
       <c r="R21" t="n">
-        <v>6664600</v>
+        <v>6664594</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3131,12 +3143,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3145,56 +3157,35 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Gruva</t>
-        </is>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Före detta kalkbrott</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129694667</t>
+          <t>https://artportalen.se/Sighting/1339311</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129694706</v>
+        <v>129694667</v>
       </c>
       <c r="B22" t="n">
         <v>93300</v>
@@ -3220,7 +3211,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3232,14 +3223,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+          <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505156</v>
+        <v>505166</v>
       </c>
       <c r="R22" t="n">
-        <v>6664597</v>
+        <v>6664600</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3323,43 +3314,39 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129694706</t>
+          <t>https://artportalen.se/Sighting/129694667</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1749447</v>
+        <v>129694706</v>
       </c>
       <c r="B23" t="n">
-        <v>93233</v>
+        <v>93300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3367,19 +3354,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norsberget, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505148</v>
+        <v>505156</v>
       </c>
       <c r="R23" t="n">
-        <v>6664594</v>
+        <v>6664597</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3403,12 +3392,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3417,35 +3406,56 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1749447</t>
+          <t>https://artportalen.se/Sighting/129694706</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694636</v>
+        <v>1749447</v>
       </c>
       <c r="B24" t="n">
         <v>93233</v>
@@ -3475,7 +3485,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3483,21 +3493,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505166</v>
+        <v>505148</v>
       </c>
       <c r="R24" t="n">
-        <v>6664600</v>
+        <v>6664594</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3521,12 +3529,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3535,59 +3543,38 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Gruva</t>
-        </is>
-      </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Före detta kalkbrott</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129694636</t>
+          <t>https://artportalen.se/Sighting/1749447</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130188803</v>
+        <v>129694636</v>
       </c>
       <c r="B25" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3595,34 +3582,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505170</v>
+        <v>505166</v>
       </c>
       <c r="R25" t="n">
-        <v>6664585</v>
+        <v>6664600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3649,12 +3647,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3663,75 +3661,97 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130188803</t>
+          <t>https://artportalen.se/Sighting/129694636</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>52432</v>
+        <v>130188803</v>
       </c>
       <c r="B26" t="n">
-        <v>58790</v>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208245</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norsen, Dlr</t>
+          <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505026</v>
+        <v>505170</v>
       </c>
       <c r="R26" t="n">
-        <v>6664372</v>
+        <v>6664585</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3755,34 +3775,19 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2013-05-03</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2013-05-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Tog bilder (bifogas)</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3790,27 +3795,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/52432</t>
+          <t>https://artportalen.se/Sighting/130188803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132227114</v>
+        <v>52432</v>
       </c>
       <c r="B27" t="n">
-        <v>107943</v>
+        <v>58790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3818,41 +3823,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219933</v>
+        <v>208245</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+          <t>Norsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505124</v>
+        <v>505026</v>
       </c>
       <c r="R27" t="n">
-        <v>6664594</v>
+        <v>6664372</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3876,48 +3881,62 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2013-05-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2013-05-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Tog bilder (bifogas)</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132227114</t>
+          <t>https://artportalen.se/Sighting/52432</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4955167</v>
+        <v>132227114</v>
       </c>
       <c r="B28" t="n">
-        <v>101326</v>
+        <v>107943</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3925,37 +3944,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219933</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norsberget, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505148</v>
+        <v>505124</v>
       </c>
       <c r="R28" t="n">
         <v>6664594</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3979,12 +4002,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3993,35 +4016,31 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4955167</t>
+          <t>https://artportalen.se/Sighting/132227114</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6778602</v>
+        <v>4955167</v>
       </c>
       <c r="B29" t="n">
         <v>101326</v>
@@ -4049,34 +4068,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norsen, Dlr</t>
+          <t>Norsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505094</v>
+        <v>505148</v>
       </c>
       <c r="R29" t="n">
-        <v>6664492</v>
+        <v>6664594</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4100,17 +4105,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2007-04-13</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2007-04-13</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4121,31 +4121,36 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mikael Ohlson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mikael Ohlson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6778602</t>
+          <t>https://artportalen.se/Sighting/4955167</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130189804</v>
+        <v>6778602</v>
       </c>
       <c r="B30" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,17 +4175,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norsberget, Dlr</t>
+          <t>Norsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505158</v>
+        <v>505094</v>
       </c>
       <c r="R30" t="n">
-        <v>6664594</v>
+        <v>6664492</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4207,12 +4226,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2007-04-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2007-04-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4227,27 +4251,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Mikael Ohlson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Mikael Ohlson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130189804</t>
+          <t>https://artportalen.se/Sighting/6778602</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5286387</v>
+        <v>130189804</v>
       </c>
       <c r="B31" t="n">
-        <v>101228</v>
+        <v>101325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4255,21 +4279,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4279,13 +4303,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505148</v>
+        <v>505158</v>
       </c>
       <c r="R31" t="n">
         <v>6664594</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4309,12 +4333,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4325,25 +4349,127 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130189804</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5286387</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5286387</t>
         </is>
@@ -4381,6 +4507,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96564</v>
+        <v>96566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96566</v>
+        <v>96579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96579</v>
+        <v>96581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96581</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96594</v>
+        <v>96595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96595</v>
+        <v>96600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96600</v>
+        <v>96602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96602</v>
+        <v>96608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96608</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96621</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>130191861</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
